--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3333333333333333</v>
+        <v>0.7875</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4</v>
+        <v>0.644927536231884</v>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>0.4375</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7875</v>
+        <v>0.7922077922077922</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="C2">
-        <v>0.644927536231884</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="D2">
-        <v>0.4375</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
